--- a/data/greif/temp/grid_db_suporte.xlsx
+++ b/data/greif/temp/grid_db_suporte.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="12">
   <si>
     <t>Cod Funcionario</t>
   </si>
@@ -47,34 +47,17 @@
     <t>Atestado Crm</t>
   </si>
   <si>
-    <t>ANDREIA CRISTIANE DE ANDRADE SILVA</t>
-  </si>
-  <si>
-    <t>052.048.979-92</t>
-  </si>
-  <si>
-    <t>Cirurgia Plástica Doutor Alexandre Wood Branco</t>
-  </si>
-  <si>
-    <t>00000</t>
-  </si>
-  <si>
-    <t>ALEXANDRE WOOD BRANCO</t>
-  </si>
-  <si>
-    <t>PR</t>
-  </si>
-  <si>
-    <t>CRM 15517</t>
+    <t>DEUSEIR WILLIAN PEREIRA DE BARROS</t>
+  </si>
+  <si>
+    <t>317.399.508-28</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <b val="0"/>
@@ -112,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -132,9 +115,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="164" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="3" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
@@ -442,14 +422,14 @@
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="41.132813" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="39.990234" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="22.280273" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="11.711426" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="24.708252" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="22.280273" bestFit="true" customWidth="true" style="0"/>
     <col min="6" max="6" width="62.41333" bestFit="true" customWidth="true" style="0"/>
     <col min="7" max="7" width="16.424561" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="25.85083" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="17.567139" bestFit="true" customWidth="true" style="0"/>
     <col min="9" max="9" width="8.140869" bestFit="true" customWidth="true" style="0"/>
     <col min="10" max="10" width="15.281982" bestFit="true" customWidth="true" style="0"/>
   </cols>
@@ -494,27 +474,15 @@
         <v>11</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="7">
-        <v>45904</v>
-      </c>
-      <c r="E2" s="8">
-        <v>1</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="D2" s="5"/>
+      <c r="E2" s="7">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
     </row>
   </sheetData>
   <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>

--- a/data/greif/temp/grid_db_suporte.xlsx
+++ b/data/greif/temp/grid_db_suporte.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="16">
   <si>
     <t>Cod Funcionario</t>
   </si>
@@ -47,17 +47,31 @@
     <t>Atestado Crm</t>
   </si>
   <si>
-    <t>DEUSEIR WILLIAN PEREIRA DE BARROS</t>
-  </si>
-  <si>
-    <t>317.399.508-28</t>
+    <t xml:space="preserve">GENEZI ELDER DOS SANTOS                                      </t>
+  </si>
+  <si>
+    <t>074.511.609-47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clínica São Vicente </t>
+  </si>
+  <si>
+    <t>Jackson Prochmann</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>5661</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <b val="0"/>
@@ -95,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -115,6 +129,9 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="164" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="3" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
@@ -422,14 +439,14 @@
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="39.990234" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="72.982178" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="22.280273" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="11.711426" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="24.708252" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="22.280273" bestFit="true" customWidth="true" style="0"/>
     <col min="6" max="6" width="62.41333" bestFit="true" customWidth="true" style="0"/>
     <col min="7" max="7" width="16.424561" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="17.567139" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="21.137695" bestFit="true" customWidth="true" style="0"/>
     <col min="9" max="9" width="8.140869" bestFit="true" customWidth="true" style="0"/>
     <col min="10" max="10" width="15.281982" bestFit="true" customWidth="true" style="0"/>
   </cols>
@@ -474,15 +491,25 @@
         <v>11</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="7">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3"/>
+      <c r="D2" s="7">
+        <v>45932</v>
+      </c>
+      <c r="E2" s="8">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
+      <c r="H2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>

--- a/data/greif/temp/grid_db_suporte.xlsx
+++ b/data/greif/temp/grid_db_suporte.xlsx
@@ -47,22 +47,22 @@
     <t>Atestado Crm</t>
   </si>
   <si>
-    <t xml:space="preserve">GENEZI ELDER DOS SANTOS                                      </t>
-  </si>
-  <si>
-    <t>074.511.609-47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clínica São Vicente </t>
-  </si>
-  <si>
-    <t>Jackson Prochmann</t>
+    <t>EULER LEANDRO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>431.986.058-65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hospital evangelico de Londrina </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mariozinho Pacheco de Freitas Camargo </t>
   </si>
   <si>
     <t>PR</t>
   </si>
   <si>
-    <t>5661</t>
+    <t>55858</t>
   </si>
 </sst>
 </file>
@@ -439,14 +439,14 @@
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="72.982178" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="30.563965" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="22.280273" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="11.711426" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="24.708252" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="22.280273" bestFit="true" customWidth="true" style="0"/>
     <col min="6" max="6" width="62.41333" bestFit="true" customWidth="true" style="0"/>
     <col min="7" max="7" width="16.424561" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="21.137695" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="45.845947" bestFit="true" customWidth="true" style="0"/>
     <col min="9" max="9" width="8.140869" bestFit="true" customWidth="true" style="0"/>
     <col min="10" max="10" width="15.281982" bestFit="true" customWidth="true" style="0"/>
   </cols>
@@ -492,7 +492,7 @@
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="7">
-        <v>45932</v>
+        <v>45922</v>
       </c>
       <c r="E2" s="8">
         <v>1</v>

--- a/data/greif/temp/grid_db_suporte.xlsx
+++ b/data/greif/temp/grid_db_suporte.xlsx
@@ -47,22 +47,22 @@
     <t>Atestado Crm</t>
   </si>
   <si>
-    <t>EULER LEANDRO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>431.986.058-65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hospital evangelico de Londrina </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mariozinho Pacheco de Freitas Camargo </t>
-  </si>
-  <si>
-    <t>PR</t>
-  </si>
-  <si>
-    <t>55858</t>
+    <t>JOAO VICTOR DA SILVA MENDES MARTINS</t>
+  </si>
+  <si>
+    <t>177.450.937-75</t>
+  </si>
+  <si>
+    <t>Clínica da Família CMS Maria Cristina Roma Paugartten</t>
+  </si>
+  <si>
+    <t>Danielle de Costa Maciel</t>
+  </si>
+  <si>
+    <t>RJ</t>
+  </si>
+  <si>
+    <t>1054953</t>
   </si>
 </sst>
 </file>
@@ -439,14 +439,14 @@
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="30.563965" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="42.418213" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="22.280273" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="11.711426" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="24.708252" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="22.280273" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="62.41333" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="63.555908" bestFit="true" customWidth="true" style="0"/>
     <col min="7" max="7" width="16.424561" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="45.845947" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="29.421387" bestFit="true" customWidth="true" style="0"/>
     <col min="9" max="9" width="8.140869" bestFit="true" customWidth="true" style="0"/>
     <col min="10" max="10" width="15.281982" bestFit="true" customWidth="true" style="0"/>
   </cols>
@@ -492,10 +492,10 @@
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="7">
-        <v>45922</v>
+        <v>45936</v>
       </c>
       <c r="E2" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>

--- a/data/greif/temp/grid_db_suporte.xlsx
+++ b/data/greif/temp/grid_db_suporte.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="12">
   <si>
     <t>Cod Funcionario</t>
   </si>
@@ -47,31 +47,17 @@
     <t>Atestado Crm</t>
   </si>
   <si>
-    <t>JOAO VICTOR DA SILVA MENDES MARTINS</t>
-  </si>
-  <si>
-    <t>177.450.937-75</t>
-  </si>
-  <si>
-    <t>Clínica da Família CMS Maria Cristina Roma Paugartten</t>
-  </si>
-  <si>
-    <t>Danielle de Costa Maciel</t>
-  </si>
-  <si>
-    <t>RJ</t>
-  </si>
-  <si>
-    <t>1054953</t>
+    <t>DEUSEIR WILLIAN PEREIRA DE BARROS</t>
+  </si>
+  <si>
+    <t>317.399.508-28</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <b val="0"/>
@@ -109,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -129,9 +115,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="164" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="3" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
@@ -439,14 +422,14 @@
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="42.418213" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="39.990234" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="22.280273" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="11.711426" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="24.708252" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="22.280273" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="63.555908" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="62.41333" bestFit="true" customWidth="true" style="0"/>
     <col min="7" max="7" width="16.424561" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="29.421387" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="17.567139" bestFit="true" customWidth="true" style="0"/>
     <col min="9" max="9" width="8.140869" bestFit="true" customWidth="true" style="0"/>
     <col min="10" max="10" width="15.281982" bestFit="true" customWidth="true" style="0"/>
   </cols>
@@ -491,25 +474,15 @@
         <v>11</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="7">
-        <v>45936</v>
-      </c>
-      <c r="E2" s="8">
-        <v>2</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>12</v>
-      </c>
+      <c r="D2" s="5"/>
+      <c r="E2" s="7">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>15</v>
-      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
     </row>
   </sheetData>
   <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>

--- a/data/greif/temp/grid_db_suporte.xlsx
+++ b/data/greif/temp/grid_db_suporte.xlsx
@@ -47,10 +47,10 @@
     <t>Atestado Crm</t>
   </si>
   <si>
-    <t>DEUSEIR WILLIAN PEREIRA DE BARROS</t>
-  </si>
-  <si>
-    <t>317.399.508-28</t>
+    <t>JOAO VINICIUS DE JESUS SANTOS</t>
+  </si>
+  <si>
+    <t>862.337.115-17</t>
   </si>
 </sst>
 </file>
@@ -422,7 +422,7 @@
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="39.990234" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="35.2771" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="22.280273" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="11.711426" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="24.708252" bestFit="true" customWidth="true" style="0"/>

--- a/data/greif/temp/grid_db_suporte.xlsx
+++ b/data/greif/temp/grid_db_suporte.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="16">
   <si>
     <t>Cod Funcionario</t>
   </si>
@@ -47,10 +47,22 @@
     <t>Atestado Crm</t>
   </si>
   <si>
-    <t>JOAO VINICIUS DE JESUS SANTOS</t>
-  </si>
-  <si>
-    <t>862.337.115-17</t>
+    <t>GUILHERME DE SOUSA</t>
+  </si>
+  <si>
+    <t>103.257.287-63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consulta médica </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingrind Schmidt tagomori </t>
+  </si>
+  <si>
+    <t>RJ</t>
+  </si>
+  <si>
+    <t>5247688-8</t>
   </si>
 </sst>
 </file>
@@ -422,14 +434,14 @@
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="35.2771" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="22.280273" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="22.280273" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="11.711426" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="24.708252" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="22.280273" bestFit="true" customWidth="true" style="0"/>
     <col min="6" max="6" width="62.41333" bestFit="true" customWidth="true" style="0"/>
     <col min="7" max="7" width="16.424561" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="17.567139" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="30.563965" bestFit="true" customWidth="true" style="0"/>
     <col min="9" max="9" width="8.140869" bestFit="true" customWidth="true" style="0"/>
     <col min="10" max="10" width="15.281982" bestFit="true" customWidth="true" style="0"/>
   </cols>
@@ -476,13 +488,21 @@
       <c r="C2" s="3"/>
       <c r="D2" s="5"/>
       <c r="E2" s="7">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
+      <c r="H2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>

--- a/data/greif/temp/grid_db_suporte.xlsx
+++ b/data/greif/temp/grid_db_suporte.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="13">
   <si>
     <t>Cod Funcionario</t>
   </si>
@@ -47,22 +47,13 @@
     <t>Atestado Crm</t>
   </si>
   <si>
-    <t>GUILHERME DE SOUSA</t>
-  </si>
-  <si>
-    <t>103.257.287-63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consulta médica </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingrind Schmidt tagomori </t>
+    <t>ALEXANDRE PEREIRA GONZALEZ</t>
+  </si>
+  <si>
+    <t>933.150.667-87</t>
   </si>
   <si>
     <t>RJ</t>
-  </si>
-  <si>
-    <t>5247688-8</t>
   </si>
 </sst>
 </file>
@@ -434,14 +425,14 @@
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="22.280273" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="31.706543" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="22.280273" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="11.711426" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="24.708252" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="22.280273" bestFit="true" customWidth="true" style="0"/>
     <col min="6" max="6" width="62.41333" bestFit="true" customWidth="true" style="0"/>
     <col min="7" max="7" width="16.424561" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="30.563965" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="17.567139" bestFit="true" customWidth="true" style="0"/>
     <col min="9" max="9" width="8.140869" bestFit="true" customWidth="true" style="0"/>
     <col min="10" max="10" width="15.281982" bestFit="true" customWidth="true" style="0"/>
   </cols>
@@ -488,21 +479,15 @@
       <c r="C2" s="3"/>
       <c r="D2" s="5"/>
       <c r="E2" s="7">
-        <v>1</v>
-      </c>
-      <c r="F2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>15</v>
-      </c>
+      <c r="J2" s="3"/>
     </row>
   </sheetData>
   <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>

--- a/data/greif/temp/grid_db_suporte.xlsx
+++ b/data/greif/temp/grid_db_suporte.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="17">
   <si>
     <t>Cod Funcionario</t>
   </si>
@@ -47,29 +47,34 @@
     <t>Atestado Crm</t>
   </si>
   <si>
-    <t>GUILHERME DE SOUSA</t>
-  </si>
-  <si>
-    <t>103.257.287-63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consulta médica </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingrind Schmidt tagomori </t>
-  </si>
-  <si>
-    <t>RJ</t>
-  </si>
-  <si>
-    <t>5247688-8</t>
+    <t>EVERTON LUIZ RODRIGUES DOS SANTOS</t>
+  </si>
+  <si>
+    <t>041.655.219-65</t>
+  </si>
+  <si>
+    <t>Concemed Centro médico e diagnóstico</t>
+  </si>
+  <si>
+    <t>M 54.5</t>
+  </si>
+  <si>
+    <t>Dr. Geraldo M. Simoni Neto</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>CRM-30184</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <b val="0"/>
@@ -107,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -127,6 +132,9 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="164" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="3" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
@@ -434,14 +442,14 @@
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="22.280273" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="39.990234" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="22.280273" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="11.711426" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="24.708252" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="22.280273" bestFit="true" customWidth="true" style="0"/>
     <col min="6" max="6" width="62.41333" bestFit="true" customWidth="true" style="0"/>
     <col min="7" max="7" width="16.424561" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="30.563965" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="31.706543" bestFit="true" customWidth="true" style="0"/>
     <col min="9" max="9" width="8.140869" bestFit="true" customWidth="true" style="0"/>
     <col min="10" max="10" width="15.281982" bestFit="true" customWidth="true" style="0"/>
   </cols>
@@ -486,22 +494,26 @@
         <v>11</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="7">
+      <c r="D2" s="7">
+        <v>45946</v>
+      </c>
+      <c r="E2" s="8">
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="3"/>
+      <c r="G2" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="H2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/data/greif/temp/grid_db_suporte.xlsx
+++ b/data/greif/temp/grid_db_suporte.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="17">
   <si>
     <t>Cod Funcionario</t>
   </si>
@@ -47,29 +47,34 @@
     <t>Atestado Crm</t>
   </si>
   <si>
-    <t>GUILHERME DE SOUSA</t>
-  </si>
-  <si>
-    <t>103.257.287-63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consulta médica </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingrind Schmidt tagomori </t>
-  </si>
-  <si>
-    <t>RJ</t>
-  </si>
-  <si>
-    <t>5247688-8</t>
+    <t>EDJANE RODRIGUES DOS SANTOS</t>
+  </si>
+  <si>
+    <t>058.925.079-55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salva vida emergências médicas </t>
+  </si>
+  <si>
+    <t>u072</t>
+  </si>
+  <si>
+    <t>Dr. Henrique F. Vaz</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>CRM-PR 55.550</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <b val="0"/>
@@ -107,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -127,6 +132,9 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="164" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="3" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
@@ -434,16 +442,16 @@
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="22.280273" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="32.991943" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="22.280273" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="11.711426" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="24.708252" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="22.280273" bestFit="true" customWidth="true" style="0"/>
     <col min="6" max="6" width="62.41333" bestFit="true" customWidth="true" style="0"/>
     <col min="7" max="7" width="16.424561" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="30.563965" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="23.422852" bestFit="true" customWidth="true" style="0"/>
     <col min="9" max="9" width="8.140869" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="15.281982" bestFit="true" customWidth="true" style="0"/>
+    <col min="10" max="10" width="16.424561" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -486,22 +494,26 @@
         <v>11</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="7">
-        <v>1</v>
+      <c r="D2" s="7">
+        <v>45964</v>
+      </c>
+      <c r="E2" s="8">
+        <v>5</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="3"/>
+      <c r="G2" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="H2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/data/greif/temp/grid_db_suporte.xlsx
+++ b/data/greif/temp/grid_db_suporte.xlsx
@@ -47,25 +47,25 @@
     <t>Atestado Crm</t>
   </si>
   <si>
-    <t>EDJANE RODRIGUES DOS SANTOS</t>
-  </si>
-  <si>
-    <t>058.925.079-55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salva vida emergências médicas </t>
-  </si>
-  <si>
-    <t>u072</t>
-  </si>
-  <si>
-    <t>Dr. Henrique F. Vaz</t>
+    <t>JULIO MARTINS NETO</t>
+  </si>
+  <si>
+    <t>045.154.169-36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atendimento on-line </t>
+  </si>
+  <si>
+    <t>M54.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Celso coelho de carvalho </t>
   </si>
   <si>
     <t>PR</t>
   </si>
   <si>
-    <t>CRM-PR 55.550</t>
+    <t>1185853</t>
   </si>
 </sst>
 </file>
@@ -442,16 +442,16 @@
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="32.991943" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="22.280273" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="22.280273" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="11.711426" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="24.708252" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="22.280273" bestFit="true" customWidth="true" style="0"/>
     <col min="6" max="6" width="62.41333" bestFit="true" customWidth="true" style="0"/>
     <col min="7" max="7" width="16.424561" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="23.422852" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="31.706543" bestFit="true" customWidth="true" style="0"/>
     <col min="9" max="9" width="8.140869" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="16.424561" bestFit="true" customWidth="true" style="0"/>
+    <col min="10" max="10" width="15.281982" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -495,10 +495,10 @@
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="7">
-        <v>45964</v>
+        <v>46062</v>
       </c>
       <c r="E2" s="8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>

--- a/data/greif/temp/grid_db_suporte.xlsx
+++ b/data/greif/temp/grid_db_suporte.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="16">
   <si>
     <t>Cod Funcionario</t>
   </si>
@@ -47,25 +47,22 @@
     <t>Atestado Crm</t>
   </si>
   <si>
-    <t>JULIO MARTINS NETO</t>
-  </si>
-  <si>
-    <t>045.154.169-36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atendimento on-line </t>
-  </si>
-  <si>
-    <t>M54.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Celso coelho de carvalho </t>
-  </si>
-  <si>
-    <t>PR</t>
-  </si>
-  <si>
-    <t>1185853</t>
+    <t>GELSON DA SILVA CEZARIO</t>
+  </si>
+  <si>
+    <t>103.082.337-51</t>
+  </si>
+  <si>
+    <t>Odontovipmaster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabiana de Araújo </t>
+  </si>
+  <si>
+    <t>RJ</t>
+  </si>
+  <si>
+    <t>50780</t>
   </si>
 </sst>
 </file>
@@ -442,14 +439,14 @@
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="22.280273" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="28.135986" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="22.280273" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="11.711426" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="24.708252" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="22.280273" bestFit="true" customWidth="true" style="0"/>
     <col min="6" max="6" width="62.41333" bestFit="true" customWidth="true" style="0"/>
     <col min="7" max="7" width="16.424561" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="31.706543" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="22.280273" bestFit="true" customWidth="true" style="0"/>
     <col min="9" max="9" width="8.140869" bestFit="true" customWidth="true" style="0"/>
     <col min="10" max="10" width="15.281982" bestFit="true" customWidth="true" style="0"/>
   </cols>
@@ -495,7 +492,7 @@
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="7">
-        <v>46062</v>
+        <v>46141</v>
       </c>
       <c r="E2" s="8">
         <v>2</v>
@@ -503,17 +500,15 @@
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
